--- a/results/regression_simulations.xlsx
+++ b/results/regression_simulations.xlsx
@@ -1946,13 +1946,13 @@
         <v>15019</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9919578196967166</v>
+        <v>0.9920925751912174</v>
       </c>
       <c r="H38" t="n">
-        <v>0.987984518969615</v>
+        <v>0.9859976207705957</v>
       </c>
       <c r="I38" t="n">
-        <v>1.000289421055503</v>
+        <v>1.00001893965827</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -1986,13 +1986,13 @@
         <v>14829</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9953095626255752</v>
+        <v>0.9948816728882458</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9890503474583214</v>
+        <v>0.9882538924871747</v>
       </c>
       <c r="I39" t="n">
-        <v>1.000059253104183</v>
+        <v>1.000077326801107</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -2026,13 +2026,13 @@
         <v>27152</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9961246823260016</v>
+        <v>0.9963625352079601</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9929016780410439</v>
+        <v>0.987956963915512</v>
       </c>
       <c r="I40" t="n">
-        <v>1.000004364586262</v>
+        <v>1.000003223418385</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -2066,13 +2066,13 @@
         <v>3000</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9978512254683621</v>
+        <v>0.9972797124207586</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9848402234955516</v>
+        <v>0.9712987010295413</v>
       </c>
       <c r="I41" t="n">
-        <v>1.000170511315188</v>
+        <v>1.00036665823951</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -2106,13 +2106,13 @@
         <v>14889</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9944415520156272</v>
+        <v>0.9942123609010742</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8248774866072576</v>
+        <v>0.8228815473563613</v>
       </c>
       <c r="I42" t="n">
-        <v>2.322110797578158</v>
+        <v>5.805129911144917</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -2146,13 +2146,13 @@
         <v>15007</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9940134680806701</v>
+        <v>0.9954611764608627</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9469685312116782</v>
+        <v>0.9482010722150388</v>
       </c>
       <c r="I43" t="n">
-        <v>1.002096889972374</v>
+        <v>1.002403957465923</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -2186,13 +2186,13 @@
         <v>27060</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9992831409813062</v>
+        <v>0.9988421717056313</v>
       </c>
       <c r="H44" t="n">
-        <v>0.930776781705729</v>
+        <v>0.9276520180551245</v>
       </c>
       <c r="I44" t="n">
-        <v>1.006318102315632</v>
+        <v>1.006121342397498</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -2226,13 +2226,13 @@
         <v>3044</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9992482708164966</v>
+        <v>0.9998091047740607</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7981040304958368</v>
+        <v>0.7993970124241848</v>
       </c>
       <c r="I45" t="n">
-        <v>1.005973608064354</v>
+        <v>1.005758088291334</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -2266,13 +2266,13 @@
         <v>15146</v>
       </c>
       <c r="G46" t="n">
-        <v>0.8119884639830761</v>
+        <v>0.8216500955523126</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9209212711390907</v>
+        <v>0.9136520706226764</v>
       </c>
       <c r="I46" t="n">
-        <v>1.008134773818888</v>
+        <v>1.008792821166351</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -2306,13 +2306,13 @@
         <v>14955</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9467451577761824</v>
+        <v>0.9502857938046688</v>
       </c>
       <c r="H47" t="n">
-        <v>0.9742654111664236</v>
+        <v>0.9722616545064202</v>
       </c>
       <c r="I47" t="n">
-        <v>1.001377450694095</v>
+        <v>1.001479867318319</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -2346,13 +2346,13 @@
         <v>26950</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9200386801046068</v>
+        <v>0.9233349128654328</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9762076343709877</v>
+        <v>0.9748951551294248</v>
       </c>
       <c r="I48" t="n">
-        <v>1.001975460201538</v>
+        <v>1.002492393277779</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -2386,13 +2386,13 @@
         <v>2949</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9127426511286715</v>
+        <v>0.9174882737485431</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9136720315574861</v>
+        <v>0.9065732376639688</v>
       </c>
       <c r="I49" t="n">
-        <v>1.052094691996402</v>
+        <v>1.155480353899409</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -2426,13 +2426,13 @@
         <v>15025</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8403815887253911</v>
+        <v>0.8485508924771544</v>
       </c>
       <c r="H50" t="n">
-        <v>0.8128093437878448</v>
+        <v>0.8163840612390241</v>
       </c>
       <c r="I50" t="n">
-        <v>1.02214712702422</v>
+        <v>1.017675389318216</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -2466,13 +2466,13 @@
         <v>14969</v>
       </c>
       <c r="G51" t="n">
-        <v>0.9625624323352961</v>
+        <v>0.9640316610702745</v>
       </c>
       <c r="H51" t="n">
-        <v>0.9443607553875579</v>
+        <v>0.9487788483956484</v>
       </c>
       <c r="I51" t="n">
-        <v>1.001755900581347</v>
+        <v>1.001300410184012</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -2506,13 +2506,13 @@
         <v>26930</v>
       </c>
       <c r="G52" t="n">
-        <v>0.9452132750521639</v>
+        <v>0.9482393818722621</v>
       </c>
       <c r="H52" t="n">
-        <v>0.9400177731313164</v>
+        <v>0.9435941401174829</v>
       </c>
       <c r="I52" t="n">
-        <v>1.002654252510728</v>
+        <v>1.001665335716958</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -2540,19 +2540,19 @@
         <v>1.2</v>
       </c>
       <c r="E53" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F53" t="n">
         <v>3076</v>
       </c>
       <c r="G53" t="n">
-        <v>0.8834419572908123</v>
+        <v>0.8897832202418889</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8430706330790317</v>
+        <v>0.8217262727131128</v>
       </c>
       <c r="I53" t="n">
-        <v>1.041508619073807</v>
+        <v>1.256285197843967</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -2586,13 +2586,13 @@
         <v>15084</v>
       </c>
       <c r="G54" t="n">
-        <v>0.9983219173779738</v>
+        <v>0.9988229295421533</v>
       </c>
       <c r="H54" t="n">
-        <v>0.7558775212509622</v>
+        <v>0.7555984252344647</v>
       </c>
       <c r="I54" t="n">
-        <v>758.7806404193774</v>
+        <v>6518.551299936097</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -2626,13 +2626,13 @@
         <v>15155</v>
       </c>
       <c r="G55" t="n">
-        <v>0.9972656069741158</v>
+        <v>0.9972454445939483</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9810138206067153</v>
+        <v>0.9819463093569755</v>
       </c>
       <c r="I55" t="n">
-        <v>1.000241418755677</v>
+        <v>1.000218990385797</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -2666,13 +2666,13 @@
         <v>26823</v>
       </c>
       <c r="G56" t="n">
-        <v>0.9986125119070717</v>
+        <v>0.9978923896628352</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7808418535573868</v>
+        <v>0.7802939158836735</v>
       </c>
       <c r="I56" t="n">
-        <v>1.098396053528578</v>
+        <v>1.090267964177336</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -2706,13 +2706,13 @@
         <v>2938</v>
       </c>
       <c r="G57" t="n">
-        <v>0.9989353572478674</v>
+        <v>0.9983240092121749</v>
       </c>
       <c r="H57" t="n">
-        <v>0.9727715470696039</v>
+        <v>0.9791680182623507</v>
       </c>
       <c r="I57" t="n">
-        <v>1.000024615694835</v>
+        <v>1.000126168021613</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -2746,13 +2746,13 @@
         <v>14914</v>
       </c>
       <c r="G58" t="n">
-        <v>0.723773541968268</v>
+        <v>0.7362262141643963</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8857109158753724</v>
+        <v>0.876034813777452</v>
       </c>
       <c r="I58" t="n">
-        <v>1.018578015530856</v>
+        <v>1.01989041150096</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -2786,13 +2786,13 @@
         <v>15032</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9751936517160587</v>
+        <v>0.9749395733645569</v>
       </c>
       <c r="H59" t="n">
-        <v>0.9697322639421517</v>
+        <v>0.9687691273614365</v>
       </c>
       <c r="I59" t="n">
-        <v>1.000023099129589</v>
+        <v>1.000008403580435</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -2826,13 +2826,13 @@
         <v>27041</v>
       </c>
       <c r="G60" t="n">
-        <v>0.7358345194745709</v>
+        <v>0.7472829039602374</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8941541520784997</v>
+        <v>0.8873493429217905</v>
       </c>
       <c r="I60" t="n">
-        <v>1.087885022638035</v>
+        <v>1.316760421733733</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
@@ -2866,13 +2866,13 @@
         <v>3013</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9940039377726435</v>
+        <v>0.9959479523282617</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9569241694930324</v>
+        <v>0.9556315704385467</v>
       </c>
       <c r="I61" t="n">
-        <v>1.000150771593799</v>
+        <v>1.000443638721338</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
@@ -2906,13 +2906,13 @@
         <v>14885</v>
       </c>
       <c r="G62" t="n">
-        <v>0.7542278348848395</v>
+        <v>0.7671433346692916</v>
       </c>
       <c r="H62" t="n">
-        <v>0.7508024766447393</v>
+        <v>0.7431948463409845</v>
       </c>
       <c r="I62" t="n">
-        <v>1.050719422017546</v>
+        <v>1.049457598530702</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -2946,13 +2946,13 @@
         <v>15115</v>
       </c>
       <c r="G63" t="n">
-        <v>0.9368379985745487</v>
+        <v>0.9412034653801428</v>
       </c>
       <c r="H63" t="n">
-        <v>0.9568382387766008</v>
+        <v>0.9498147788237674</v>
       </c>
       <c r="I63" t="n">
-        <v>1.000789988773504</v>
+        <v>1.002581338132676</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -2980,23 +2980,23 @@
         <v>1.2</v>
       </c>
       <c r="E64" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F64" t="n">
         <v>27010</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7191787828334686</v>
+        <v>0.7350016659038414</v>
       </c>
       <c r="H64" t="n">
-        <v>0.8142934498096983</v>
+        <v>0.7940036856521422</v>
       </c>
       <c r="I64" t="n">
-        <v>11.37039670206993</v>
+        <v>673.4282019907181</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>no bias</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -3026,13 +3026,13 @@
         <v>2990</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9717698536595885</v>
+        <v>0.9736022517946273</v>
       </c>
       <c r="H65" t="n">
-        <v>0.9604171902689619</v>
+        <v>0.9626858311976589</v>
       </c>
       <c r="I65" t="n">
-        <v>0.9997382620862627</v>
+        <v>1.000188545078717</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
@@ -3066,13 +3066,13 @@
         <v>15065</v>
       </c>
       <c r="G66" t="n">
-        <v>0.999616255837763</v>
+        <v>0.9995204485908085</v>
       </c>
       <c r="H66" t="n">
-        <v>0.8361829530881171</v>
+        <v>0.8421876223533928</v>
       </c>
       <c r="I66" t="n">
-        <v>1.643890310133469</v>
+        <v>2.255052111370254</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -3106,13 +3106,13 @@
         <v>14975</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9981698375812407</v>
+        <v>0.9991407811681392</v>
       </c>
       <c r="H67" t="n">
-        <v>0.9309434005910959</v>
+        <v>0.9247034928059481</v>
       </c>
       <c r="I67" t="n">
-        <v>1.004339187473257</v>
+        <v>1.004820006463808</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
@@ -3146,13 +3146,13 @@
         <v>27072</v>
       </c>
       <c r="G68" t="n">
-        <v>0.9998571547065909</v>
+        <v>0.9996212858482088</v>
       </c>
       <c r="H68" t="n">
-        <v>0.9090136724230503</v>
+        <v>0.9029932601014895</v>
       </c>
       <c r="I68" t="n">
-        <v>1.013229813538772</v>
+        <v>1.013590896193212</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
@@ -3180,19 +3180,19 @@
         <v>1</v>
       </c>
       <c r="E69" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F69" t="n">
         <v>2888</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9951901898721001</v>
+        <v>0.9964108519562331</v>
       </c>
       <c r="H69" t="n">
-        <v>0.9553472232928264</v>
+        <v>0.887314790313411</v>
       </c>
       <c r="I69" t="n">
-        <v>1.000367665493322</v>
+        <v>1.033968320006903</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
@@ -3226,13 +3226,13 @@
         <v>15166</v>
       </c>
       <c r="G70" t="n">
-        <v>0.8192407184813217</v>
+        <v>0.8360402802892168</v>
       </c>
       <c r="H70" t="n">
-        <v>0.9321254502300406</v>
+        <v>0.9281407397210855</v>
       </c>
       <c r="I70" t="n">
-        <v>1.006732741509041</v>
+        <v>1.006736451253756</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
@@ -3266,13 +3266,13 @@
         <v>14922</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9330204694448418</v>
+        <v>0.9317131092214592</v>
       </c>
       <c r="H71" t="n">
-        <v>0.9723587622301793</v>
+        <v>0.970830943976429</v>
       </c>
       <c r="I71" t="n">
-        <v>1.001702640717164</v>
+        <v>1.002475188989432</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
@@ -3306,13 +3306,13 @@
         <v>26882</v>
       </c>
       <c r="G72" t="n">
-        <v>0.8901082205238824</v>
+        <v>0.8870362453328035</v>
       </c>
       <c r="H72" t="n">
-        <v>0.963497967508548</v>
+        <v>0.9569903271970099</v>
       </c>
       <c r="I72" t="n">
-        <v>1.005400821361521</v>
+        <v>1.00763779367452</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
@@ -3337,22 +3337,22 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E73" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F73" t="n">
         <v>3030</v>
       </c>
       <c r="G73" t="n">
-        <v>0.9769690669529055</v>
+        <v>0.9340697478194249</v>
       </c>
       <c r="H73" t="n">
-        <v>0.9662084058943474</v>
+        <v>0.9353036391815922</v>
       </c>
       <c r="I73" t="n">
-        <v>0.9999743788279232</v>
+        <v>0.9995795096877269</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
@@ -3377,22 +3377,22 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E74" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F74" t="n">
         <v>14985</v>
       </c>
       <c r="G74" t="n">
-        <v>0.922732771418998</v>
+        <v>0.8409340786287354</v>
       </c>
       <c r="H74" t="n">
-        <v>0.8254746160421097</v>
+        <v>0.8777047227049084</v>
       </c>
       <c r="I74" t="n">
-        <v>2.200349421312612</v>
+        <v>1.048893904464671</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
@@ -3426,13 +3426,13 @@
         <v>15155</v>
       </c>
       <c r="G75" t="n">
-        <v>0.9577115549083061</v>
+        <v>0.9307793236566968</v>
       </c>
       <c r="H75" t="n">
-        <v>0.919667862100419</v>
+        <v>0.9400967552944872</v>
       </c>
       <c r="I75" t="n">
-        <v>1.005375908400452</v>
+        <v>1.002634273986078</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
@@ -3466,13 +3466,13 @@
         <v>26883</v>
       </c>
       <c r="G76" t="n">
-        <v>0.9367195841045574</v>
+        <v>0.896296747007883</v>
       </c>
       <c r="H76" t="n">
-        <v>0.9045743492199277</v>
+        <v>0.9297996966669938</v>
       </c>
       <c r="I76" t="n">
-        <v>1.014046754044824</v>
+        <v>1.005933412358131</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
@@ -3500,19 +3500,19 @@
         <v>1.2</v>
       </c>
       <c r="E77" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F77" t="n">
         <v>2977</v>
       </c>
       <c r="G77" t="n">
-        <v>0.9244928467160334</v>
+        <v>0.9410901745196821</v>
       </c>
       <c r="H77" t="n">
-        <v>0.9430740095920082</v>
+        <v>0.9005288284427172</v>
       </c>
       <c r="I77" t="n">
-        <v>1.000738387186791</v>
+        <v>1.004985763440368</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
@@ -3546,13 +3546,13 @@
         <v>14876</v>
       </c>
       <c r="G78" t="n">
-        <v>0.9974867253726223</v>
+        <v>0.9957795844999775</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8849836007718157</v>
+        <v>0.936086871076926</v>
       </c>
       <c r="I78" t="n">
-        <v>1.036980473632359</v>
+        <v>1.005758893595448</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
@@ -3586,13 +3586,13 @@
         <v>15052</v>
       </c>
       <c r="G79" t="n">
-        <v>0.998610590376364</v>
+        <v>0.9992745133170408</v>
       </c>
       <c r="H79" t="n">
-        <v>0.8819173360847817</v>
+        <v>0.8379925893507784</v>
       </c>
       <c r="I79" t="n">
-        <v>1.011289799906666</v>
+        <v>1.021195989111104</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
@@ -3620,19 +3620,19 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F80" t="n">
         <v>27062</v>
       </c>
       <c r="G80" t="n">
-        <v>0.9965279646459908</v>
+        <v>0.9944069845581788</v>
       </c>
       <c r="H80" t="n">
-        <v>0.9865215062998796</v>
+        <v>0.9046088581118495</v>
       </c>
       <c r="I80" t="n">
-        <v>1.000271425034128</v>
+        <v>1.027529685839791</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
@@ -3666,13 +3666,13 @@
         <v>3010</v>
       </c>
       <c r="G81" t="n">
-        <v>0.9942977644894654</v>
+        <v>0.9941584615754212</v>
       </c>
       <c r="H81" t="n">
-        <v>0.9162317268390762</v>
+        <v>0.8801579411944297</v>
       </c>
       <c r="I81" t="n">
-        <v>1.0005000309973</v>
+        <v>1.000353301098392</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
@@ -3706,13 +3706,13 @@
         <v>15113</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8759234808630245</v>
+        <v>0.9350645416864305</v>
       </c>
       <c r="H82" t="n">
-        <v>0.9492795678575384</v>
+        <v>0.9687129374870002</v>
       </c>
       <c r="I82" t="n">
-        <v>1.003341856497571</v>
+        <v>1.001017656133815</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
@@ -3746,13 +3746,13 @@
         <v>14969</v>
       </c>
       <c r="G83" t="n">
-        <v>0.8901764105805288</v>
+        <v>0.8534418988114959</v>
       </c>
       <c r="H83" t="n">
-        <v>0.9460279201414223</v>
+        <v>0.9208373666703207</v>
       </c>
       <c r="I83" t="n">
-        <v>1.006766341331794</v>
+        <v>1.033943813166195</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
@@ -3777,22 +3777,22 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F84" t="n">
         <v>27036</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9949572888065091</v>
+        <v>0.904683874333883</v>
       </c>
       <c r="H84" t="n">
-        <v>0.9821545407068247</v>
+        <v>0.9480857378145875</v>
       </c>
       <c r="I84" t="n">
-        <v>1.000179854381879</v>
+        <v>1.005239127241987</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
@@ -3826,13 +3826,13 @@
         <v>2882</v>
       </c>
       <c r="G85" t="n">
-        <v>0.9586237426108575</v>
+        <v>0.9429692026768146</v>
       </c>
       <c r="H85" t="n">
-        <v>0.9554380953509948</v>
+        <v>0.9373808564389238</v>
       </c>
       <c r="I85" t="n">
-        <v>1.001774240899069</v>
+        <v>1.012175052127535</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
@@ -3857,22 +3857,22 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E86" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F86" t="n">
         <v>15002</v>
       </c>
       <c r="G86" t="n">
-        <v>0.9858539667624947</v>
+        <v>0.9339770268267673</v>
       </c>
       <c r="H86" t="n">
-        <v>0.8699248937608393</v>
+        <v>0.9439585568030998</v>
       </c>
       <c r="I86" t="n">
-        <v>1.054858383200627</v>
+        <v>1.002037093099868</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
@@ -3906,13 +3906,13 @@
         <v>14883</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8687699099202048</v>
+        <v>0.8520574280598137</v>
       </c>
       <c r="H87" t="n">
-        <v>0.8700349723882852</v>
+        <v>0.873669570040673</v>
       </c>
       <c r="I87" t="n">
-        <v>1.008980137982187</v>
+        <v>1.005726014086375</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
@@ -3940,19 +3940,19 @@
         <v>1.2</v>
       </c>
       <c r="E88" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F88" t="n">
         <v>27086</v>
       </c>
       <c r="G88" t="n">
-        <v>0.8495498160496485</v>
+        <v>0.9015001180064557</v>
       </c>
       <c r="H88" t="n">
-        <v>0.9852067366482816</v>
+        <v>0.9328083374334877</v>
       </c>
       <c r="I88" t="n">
-        <v>1.000075549799262</v>
+        <v>1.004556755430032</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
@@ -3986,13 +3986,13 @@
         <v>3029</v>
       </c>
       <c r="G89" t="n">
-        <v>0.9448802921828854</v>
+        <v>0.9373640211222204</v>
       </c>
       <c r="H89" t="n">
-        <v>0.8897593003419617</v>
+        <v>0.8973148552916039</v>
       </c>
       <c r="I89" t="n">
-        <v>1.000050609888789</v>
+        <v>0.9990971388839812</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -4026,13 +4026,13 @@
         <v>14980</v>
       </c>
       <c r="G90" t="n">
-        <v>0.9967234799732608</v>
+        <v>0.9968968413343047</v>
       </c>
       <c r="H90" t="n">
-        <v>0.9007760157831927</v>
+        <v>0.9008083854306553</v>
       </c>
       <c r="I90" t="n">
-        <v>1.007769352776936</v>
+        <v>1.00746977934727</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
@@ -4066,13 +4066,13 @@
         <v>14837</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9966657550960653</v>
+        <v>0.9961293820617673</v>
       </c>
       <c r="H91" t="n">
-        <v>0.9012713697204894</v>
+        <v>0.9009912028077843</v>
       </c>
       <c r="I91" t="n">
-        <v>1.008228301648465</v>
+        <v>1.006940628188383</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
@@ -4106,13 +4106,13 @@
         <v>27016</v>
       </c>
       <c r="G92" t="n">
-        <v>0.9983962629125909</v>
+        <v>0.9988647755675754</v>
       </c>
       <c r="H92" t="n">
-        <v>0.8203184893118461</v>
+        <v>0.8201090871256443</v>
       </c>
       <c r="I92" t="n">
-        <v>5.603634734669539</v>
+        <v>16.24188994897384</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
@@ -4146,13 +4146,13 @@
         <v>3167</v>
       </c>
       <c r="G93" t="n">
-        <v>0.9963405695612738</v>
+        <v>0.9960125356906853</v>
       </c>
       <c r="H93" t="n">
-        <v>0.7736605525993657</v>
+        <v>0.7735116938632006</v>
       </c>
       <c r="I93" t="n">
-        <v>1.006655144924276</v>
+        <v>1.004606544017236</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
@@ -4186,13 +4186,13 @@
         <v>14889</v>
       </c>
       <c r="G94" t="n">
-        <v>0.9007805089256351</v>
+        <v>0.9048046270350346</v>
       </c>
       <c r="H94" t="n">
-        <v>0.957064644750481</v>
+        <v>0.9505876215283892</v>
       </c>
       <c r="I94" t="n">
-        <v>1.003442799536188</v>
+        <v>1.004793933273245</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
@@ -4226,13 +4226,13 @@
         <v>15216</v>
       </c>
       <c r="G95" t="n">
-        <v>0.904980584730079</v>
+        <v>0.9080292043798411</v>
       </c>
       <c r="H95" t="n">
-        <v>0.9639259529202858</v>
+        <v>0.9581789986123992</v>
       </c>
       <c r="I95" t="n">
-        <v>1.002962324166915</v>
+        <v>1.004287257294374</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
@@ -4266,13 +4266,13 @@
         <v>26926</v>
       </c>
       <c r="G96" t="n">
-        <v>0.7851763538256336</v>
+        <v>0.7935338230313058</v>
       </c>
       <c r="H96" t="n">
-        <v>0.9211351021887179</v>
+        <v>0.9106614533186173</v>
       </c>
       <c r="I96" t="n">
-        <v>1.016428552325727</v>
+        <v>1.019348955671136</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
@@ -4306,13 +4306,13 @@
         <v>2969</v>
       </c>
       <c r="G97" t="n">
-        <v>0.8955645344708607</v>
+        <v>0.9006006067740565</v>
       </c>
       <c r="H97" t="n">
-        <v>0.9019934749880828</v>
+        <v>0.8895866669713981</v>
       </c>
       <c r="I97" t="n">
-        <v>1.132442860656416</v>
+        <v>1.866940711643666</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
@@ -4346,13 +4346,13 @@
         <v>14972</v>
       </c>
       <c r="G98" t="n">
-        <v>0.9209935397221699</v>
+        <v>0.9239573331560521</v>
       </c>
       <c r="H98" t="n">
-        <v>0.8951360745590445</v>
+        <v>0.9007484232390939</v>
       </c>
       <c r="I98" t="n">
-        <v>1.0140547580961</v>
+        <v>1.010096738377645</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
@@ -4386,13 +4386,13 @@
         <v>15087</v>
       </c>
       <c r="G99" t="n">
-        <v>0.9263509953679503</v>
+        <v>0.9305530716123638</v>
       </c>
       <c r="H99" t="n">
-        <v>0.8996732623773005</v>
+        <v>0.9048000257104569</v>
       </c>
       <c r="I99" t="n">
-        <v>1.012669167225567</v>
+        <v>1.009362864126583</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
@@ -4426,17 +4426,17 @@
         <v>26955</v>
       </c>
       <c r="G100" t="n">
-        <v>0.8040311745506569</v>
+        <v>0.8135791399852927</v>
       </c>
       <c r="H100" t="n">
-        <v>0.7954591933114292</v>
+        <v>0.800010159620164</v>
       </c>
       <c r="I100" t="n">
-        <v>1.066028768884229</v>
+        <v>1.055553964630626</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>no bias</t>
         </is>
       </c>
     </row>
@@ -4460,23 +4460,23 @@
         <v>1.2</v>
       </c>
       <c r="E101" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F101" t="n">
         <v>2986</v>
       </c>
       <c r="G101" t="n">
-        <v>0.8558992292170211</v>
+        <v>0.8634578210132631</v>
       </c>
       <c r="H101" t="n">
-        <v>0.8030429073044402</v>
+        <v>0.7841040791869491</v>
       </c>
       <c r="I101" t="n">
-        <v>1.419268040131866</v>
+        <v>5.827972209627846</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>no bias</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -4506,13 +4506,13 @@
         <v>14987</v>
       </c>
       <c r="G102" t="n">
-        <v>0.9991196487060813</v>
+        <v>0.9988479379570274</v>
       </c>
       <c r="H102" t="n">
-        <v>0.8919091576690383</v>
+        <v>0.884598039608454</v>
       </c>
       <c r="I102" t="n">
-        <v>1.009383367087931</v>
+        <v>1.009275034040055</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
@@ -4546,13 +4546,13 @@
         <v>15093</v>
       </c>
       <c r="G103" t="n">
-        <v>0.9970763419880185</v>
+        <v>0.9969379240651367</v>
       </c>
       <c r="H103" t="n">
-        <v>0.8872389165738891</v>
+        <v>0.8816348518731322</v>
       </c>
       <c r="I103" t="n">
-        <v>1.01099587167161</v>
+        <v>1.011004043613672</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
@@ -4586,13 +4586,13 @@
         <v>26912</v>
       </c>
       <c r="G104" t="n">
-        <v>0.9994371249823941</v>
+        <v>0.9993865934964485</v>
       </c>
       <c r="H104" t="n">
-        <v>0.8428896778763629</v>
+        <v>0.8493329133663253</v>
       </c>
       <c r="I104" t="n">
-        <v>1.589047312041925</v>
+        <v>1.740979076009732</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
@@ -4620,19 +4620,19 @@
         <v>1</v>
       </c>
       <c r="E105" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F105" t="n">
         <v>3008</v>
       </c>
       <c r="G105" t="n">
-        <v>0.9972158791708399</v>
+        <v>0.9975948162331117</v>
       </c>
       <c r="H105" t="n">
-        <v>0.9790840851850595</v>
+        <v>0.9125140965870018</v>
       </c>
       <c r="I105" t="n">
-        <v>1.00005937240188</v>
+        <v>1.014621334337294</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
@@ -4666,13 +4666,13 @@
         <v>15027</v>
       </c>
       <c r="G106" t="n">
-        <v>0.8839717193954029</v>
+        <v>0.8837868867072191</v>
       </c>
       <c r="H106" t="n">
-        <v>0.9569423864830102</v>
+        <v>0.9499052695623653</v>
       </c>
       <c r="I106" t="n">
-        <v>1.005287945387487</v>
+        <v>1.00852591399107</v>
       </c>
       <c r="J106" t="inlineStr">
         <is>
@@ -4706,13 +4706,13 @@
         <v>15063</v>
       </c>
       <c r="G107" t="n">
-        <v>0.8868434002397531</v>
+        <v>0.8873336020976413</v>
       </c>
       <c r="H107" t="n">
-        <v>0.9530811890572864</v>
+        <v>0.9459207195345868</v>
       </c>
       <c r="I107" t="n">
-        <v>1.004274830413409</v>
+        <v>1.006691973634754</v>
       </c>
       <c r="J107" t="inlineStr">
         <is>
@@ -4746,13 +4746,13 @@
         <v>26915</v>
       </c>
       <c r="G108" t="n">
-        <v>0.8038340404993489</v>
+        <v>0.8226781226053784</v>
       </c>
       <c r="H108" t="n">
-        <v>0.9316425775331154</v>
+        <v>0.9273248501557286</v>
       </c>
       <c r="I108" t="n">
-        <v>1.0128153875584</v>
+        <v>1.012873811825406</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
@@ -4777,22 +4777,22 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E109" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F109" t="n">
         <v>2995</v>
       </c>
       <c r="G109" t="n">
-        <v>0.9918471167735109</v>
+        <v>0.9494193485583814</v>
       </c>
       <c r="H109" t="n">
-        <v>0.9838341356363437</v>
+        <v>0.9576237963623536</v>
       </c>
       <c r="I109" t="n">
-        <v>1.000004560197356</v>
+        <v>0.9999075515012179</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
@@ -4826,13 +4826,13 @@
         <v>14910</v>
       </c>
       <c r="G110" t="n">
-        <v>0.932666062055225</v>
+        <v>0.8887822791861125</v>
       </c>
       <c r="H110" t="n">
-        <v>0.8742898688881696</v>
+        <v>0.9085350061988978</v>
       </c>
       <c r="I110" t="n">
-        <v>1.012040866061336</v>
+        <v>1.003780374315123</v>
       </c>
       <c r="J110" t="inlineStr">
         <is>
@@ -4866,13 +4866,13 @@
         <v>15009</v>
       </c>
       <c r="G111" t="n">
-        <v>0.9322007804784617</v>
+        <v>0.8894323334432166</v>
       </c>
       <c r="H111" t="n">
-        <v>0.8746914823597329</v>
+        <v>0.9096462408357134</v>
       </c>
       <c r="I111" t="n">
-        <v>1.01175887562484</v>
+        <v>1.003819605045051</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
@@ -4897,22 +4897,22 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E112" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F112" t="n">
         <v>27116</v>
       </c>
       <c r="G112" t="n">
-        <v>0.9125141828640116</v>
+        <v>0.8258020424055192</v>
       </c>
       <c r="H112" t="n">
-        <v>0.8267142941066984</v>
+        <v>0.8815359147939601</v>
       </c>
       <c r="I112" t="n">
-        <v>2.873170373808582</v>
+        <v>1.064827805558619</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
@@ -4940,19 +4940,19 @@
         <v>1.2</v>
       </c>
       <c r="E113" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F113" t="n">
         <v>2965</v>
       </c>
       <c r="G113" t="n">
-        <v>0.931154224050317</v>
+        <v>0.9573067474102338</v>
       </c>
       <c r="H113" t="n">
-        <v>0.9734817518641472</v>
+        <v>0.9214768711777561</v>
       </c>
       <c r="I113" t="n">
-        <v>0.9997194113137413</v>
+        <v>1.001469343340949</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
@@ -4986,13 +4986,13 @@
         <v>14938</v>
       </c>
       <c r="G114" t="n">
-        <v>0.9990330313771916</v>
+        <v>0.9985658139715855</v>
       </c>
       <c r="H114" t="n">
-        <v>0.7925565366224774</v>
+        <v>0.792854901991176</v>
       </c>
       <c r="I114" t="n">
-        <v>25.18617921761305</v>
+        <v>111.4405872983647</v>
       </c>
       <c r="J114" t="inlineStr">
         <is>
@@ -5026,13 +5026,13 @@
         <v>15174</v>
       </c>
       <c r="G115" t="n">
-        <v>0.9988535440336811</v>
+        <v>0.9983569147381116</v>
       </c>
       <c r="H115" t="n">
-        <v>0.7951872231042501</v>
+        <v>0.7959669403238453</v>
       </c>
       <c r="I115" t="n">
-        <v>1.042907794441279</v>
+        <v>1.038161214399945</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
@@ -5066,13 +5066,13 @@
         <v>26903</v>
       </c>
       <c r="G116" t="n">
-        <v>0.999196032141431</v>
+        <v>0.9985853365486308</v>
       </c>
       <c r="H116" t="n">
-        <v>0.982647696788771</v>
+        <v>0.9825561210422604</v>
       </c>
       <c r="I116" t="n">
-        <v>1.000445707701745</v>
+        <v>1.000396090271862</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
@@ -5106,13 +5106,13 @@
         <v>2985</v>
       </c>
       <c r="G117" t="n">
-        <v>0.9976239042625706</v>
+        <v>0.9970987323102786</v>
       </c>
       <c r="H117" t="n">
-        <v>0.9787506411261463</v>
+        <v>0.9758507996958292</v>
       </c>
       <c r="I117" t="n">
-        <v>1.000006395574805</v>
+        <v>0.9999596144555671</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
@@ -5146,13 +5146,13 @@
         <v>14748</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7725542214056909</v>
+        <v>0.7849325604105214</v>
       </c>
       <c r="H118" t="n">
-        <v>0.8928792862613336</v>
+        <v>0.8865646451273835</v>
       </c>
       <c r="I118" t="n">
-        <v>1.014585627547275</v>
+        <v>1.015088648601997</v>
       </c>
       <c r="J118" t="inlineStr">
         <is>
@@ -5186,13 +5186,13 @@
         <v>15248</v>
       </c>
       <c r="G119" t="n">
-        <v>0.792582641662599</v>
+        <v>0.8036235227803915</v>
       </c>
       <c r="H119" t="n">
-        <v>0.906757580222407</v>
+        <v>0.8974218792682865</v>
       </c>
       <c r="I119" t="n">
-        <v>1.071247731248186</v>
+        <v>1.249313504757012</v>
       </c>
       <c r="J119" t="inlineStr">
         <is>
@@ -5226,13 +5226,13 @@
         <v>27022</v>
       </c>
       <c r="G120" t="n">
-        <v>0.9872169201442187</v>
+        <v>0.9881838070342348</v>
       </c>
       <c r="H120" t="n">
-        <v>0.9805507426030492</v>
+        <v>0.9819782999071131</v>
       </c>
       <c r="I120" t="n">
-        <v>1.000466744788461</v>
+        <v>1.000454898798515</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
@@ -5266,13 +5266,13 @@
         <v>2982</v>
       </c>
       <c r="G121" t="n">
-        <v>0.9941778315753069</v>
+        <v>0.9943695620577533</v>
       </c>
       <c r="H121" t="n">
-        <v>0.9651607642134237</v>
+        <v>0.9707936114158926</v>
       </c>
       <c r="I121" t="n">
-        <v>1.000062516992355</v>
+        <v>1.000054354311359</v>
       </c>
       <c r="J121" t="inlineStr">
         <is>
@@ -5306,13 +5306,13 @@
         <v>15212</v>
       </c>
       <c r="G122" t="n">
-        <v>0.7952381364144019</v>
+        <v>0.8057458157404972</v>
       </c>
       <c r="H122" t="n">
-        <v>0.778911007835002</v>
+        <v>0.7782048654219617</v>
       </c>
       <c r="I122" t="n">
-        <v>1.039832132812527</v>
+        <v>1.036062692876173</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
@@ -5340,19 +5340,19 @@
         <v>1.2</v>
       </c>
       <c r="E123" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F123" t="n">
         <v>14845</v>
       </c>
       <c r="G123" t="n">
-        <v>0.7643305897555595</v>
+        <v>0.774719668075129</v>
       </c>
       <c r="H123" t="n">
-        <v>0.8283455296545632</v>
+        <v>0.8074882447733029</v>
       </c>
       <c r="I123" t="n">
-        <v>1.613278025647972</v>
+        <v>13.03072003275577</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
@@ -5386,13 +5386,13 @@
         <v>26962</v>
       </c>
       <c r="G124" t="n">
-        <v>0.9797351436381923</v>
+        <v>0.9800046763241766</v>
       </c>
       <c r="H124" t="n">
-        <v>0.9422944355863773</v>
+        <v>0.9524840488966448</v>
       </c>
       <c r="I124" t="n">
-        <v>0.9999773550996975</v>
+        <v>1.001055227776352</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
@@ -5426,13 +5426,13 @@
         <v>2981</v>
       </c>
       <c r="G125" t="n">
-        <v>0.9883321734287214</v>
+        <v>0.9873092729924787</v>
       </c>
       <c r="H125" t="n">
-        <v>0.95881273156564</v>
+        <v>0.955990314544787</v>
       </c>
       <c r="I125" t="n">
-        <v>1.00013842713518</v>
+        <v>1.000081169740468</v>
       </c>
       <c r="J125" t="inlineStr">
         <is>
@@ -5466,13 +5466,13 @@
         <v>14920</v>
       </c>
       <c r="G126" t="n">
-        <v>0.9973549820108287</v>
+        <v>0.9964490633086359</v>
       </c>
       <c r="H126" t="n">
-        <v>0.8622581939629217</v>
+        <v>0.8893112129656204</v>
       </c>
       <c r="I126" t="n">
-        <v>1.131995128488825</v>
+        <v>1.048287408132375</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
@@ -5500,19 +5500,19 @@
         <v>1</v>
       </c>
       <c r="E127" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F127" t="n">
         <v>15154</v>
       </c>
       <c r="G127" t="n">
-        <v>0.9919709929768724</v>
+        <v>0.9934637496048949</v>
       </c>
       <c r="H127" t="n">
-        <v>0.9688541390473452</v>
+        <v>0.8888928780478025</v>
       </c>
       <c r="I127" t="n">
-        <v>1.001375356240407</v>
+        <v>1.051195543188183</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
@@ -5546,13 +5546,13 @@
         <v>26929</v>
       </c>
       <c r="G128" t="n">
-        <v>0.9948492935577481</v>
+        <v>0.9965737978117111</v>
       </c>
       <c r="H128" t="n">
-        <v>0.883647153946503</v>
+        <v>0.8488441437294213</v>
       </c>
       <c r="I128" t="n">
-        <v>1.022978848705262</v>
+        <v>1.037089928149728</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
@@ -5586,13 +5586,13 @@
         <v>2997</v>
       </c>
       <c r="G129" t="n">
-        <v>0.9990055694228004</v>
+        <v>0.9981681194285106</v>
       </c>
       <c r="H129" t="n">
-        <v>0.9086490718080414</v>
+        <v>0.8866926807060517</v>
       </c>
       <c r="I129" t="n">
-        <v>1.000266116178304</v>
+        <v>1.000042863024952</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
@@ -5626,13 +5626,13 @@
         <v>14941</v>
       </c>
       <c r="G130" t="n">
-        <v>0.8586720946480003</v>
+        <v>0.8968244925500838</v>
       </c>
       <c r="H130" t="n">
-        <v>0.9395192591108432</v>
+        <v>0.9455117758706634</v>
       </c>
       <c r="I130" t="n">
-        <v>1.004497713429958</v>
+        <v>1.003088555467795</v>
       </c>
       <c r="J130" t="inlineStr">
         <is>
@@ -5657,22 +5657,22 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E131" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F131" t="n">
         <v>14774</v>
       </c>
       <c r="G131" t="n">
-        <v>0.9649208123637663</v>
+        <v>0.8847639310150071</v>
       </c>
       <c r="H131" t="n">
-        <v>0.9797136291942923</v>
+        <v>0.9400468194055204</v>
       </c>
       <c r="I131" t="n">
-        <v>1.000331007921798</v>
+        <v>1.003688817742437</v>
       </c>
       <c r="J131" t="inlineStr">
         <is>
@@ -5706,13 +5706,13 @@
         <v>27232</v>
       </c>
       <c r="G132" t="n">
-        <v>0.8639987412867687</v>
+        <v>0.8315046805781925</v>
       </c>
       <c r="H132" t="n">
-        <v>0.9468712382409182</v>
+        <v>0.9230462184380629</v>
       </c>
       <c r="I132" t="n">
-        <v>1.010404230845587</v>
+        <v>1.030426633915777</v>
       </c>
       <c r="J132" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>3053</v>
       </c>
       <c r="G133" t="n">
-        <v>0.9612374007402272</v>
+        <v>0.9527900276337391</v>
       </c>
       <c r="H133" t="n">
-        <v>0.9645593250261587</v>
+        <v>0.9557945877133663</v>
       </c>
       <c r="I133" t="n">
-        <v>1.000498389157742</v>
+        <v>1.001922817528541</v>
       </c>
       <c r="J133" t="inlineStr">
         <is>
@@ -5777,22 +5777,22 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E134" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F134" t="n">
         <v>15178</v>
       </c>
       <c r="G134" t="n">
-        <v>0.9697464765045914</v>
+        <v>0.890848996969953</v>
       </c>
       <c r="H134" t="n">
-        <v>0.8528859766439527</v>
+        <v>0.9129464193289246</v>
       </c>
       <c r="I134" t="n">
-        <v>1.144082919828736</v>
+        <v>1.008659766362745</v>
       </c>
       <c r="J134" t="inlineStr">
         <is>
@@ -5820,19 +5820,19 @@
         <v>1.2</v>
       </c>
       <c r="E135" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F135" t="n">
         <v>14871</v>
       </c>
       <c r="G135" t="n">
-        <v>0.8569900774467178</v>
+        <v>0.8938642023164798</v>
       </c>
       <c r="H135" t="n">
-        <v>0.9578591653683218</v>
+        <v>0.9151459862203752</v>
       </c>
       <c r="I135" t="n">
-        <v>1.000493360383156</v>
+        <v>1.007317705291633</v>
       </c>
       <c r="J135" t="inlineStr">
         <is>
@@ -5866,13 +5866,13 @@
         <v>26905</v>
       </c>
       <c r="G136" t="n">
-        <v>0.8654605323771617</v>
+        <v>0.8323578257518154</v>
       </c>
       <c r="H136" t="n">
-        <v>0.8643864076547677</v>
+        <v>0.8789674405395258</v>
       </c>
       <c r="I136" t="n">
-        <v>1.023942245994131</v>
+        <v>1.013965389532274</v>
       </c>
       <c r="J136" t="inlineStr">
         <is>
@@ -5906,13 +5906,13 @@
         <v>3046</v>
       </c>
       <c r="G137" t="n">
-        <v>0.9636145961314352</v>
+        <v>0.9548969010743543</v>
       </c>
       <c r="H137" t="n">
-        <v>0.9163082660683701</v>
+        <v>0.9329520655057774</v>
       </c>
       <c r="I137" t="n">
-        <v>0.9998856350870258</v>
+        <v>0.9993309345451326</v>
       </c>
       <c r="J137" t="inlineStr">
         <is>
@@ -5946,13 +5946,13 @@
         <v>15019</v>
       </c>
       <c r="G138" t="n">
-        <v>0.9919578196967166</v>
+        <v>0.9920925751912174</v>
       </c>
       <c r="H138" t="n">
-        <v>0.9846518618940325</v>
+        <v>0.9814052425186182</v>
       </c>
       <c r="I138" t="n">
-        <v>1.000056016998698</v>
+        <v>1.000055251969162</v>
       </c>
       <c r="J138" t="inlineStr">
         <is>
@@ -5986,13 +5986,13 @@
         <v>14829</v>
       </c>
       <c r="G139" t="n">
-        <v>0.9953095626255752</v>
+        <v>0.9948816728882458</v>
       </c>
       <c r="H139" t="n">
-        <v>0.984847929848073</v>
+        <v>0.9829717125770837</v>
       </c>
       <c r="I139" t="n">
-        <v>1.000029174119583</v>
+        <v>1.000040008973625</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
@@ -6026,13 +6026,13 @@
         <v>27152</v>
       </c>
       <c r="G140" t="n">
-        <v>0.9961246823260016</v>
+        <v>0.9963625352079601</v>
       </c>
       <c r="H140" t="n">
-        <v>0.9902124057558691</v>
+        <v>0.9842386974490636</v>
       </c>
       <c r="I140" t="n">
-        <v>1.00000687597842</v>
+        <v>1.000007483429449</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
@@ -6066,13 +6066,13 @@
         <v>3000</v>
       </c>
       <c r="G141" t="n">
-        <v>0.9978512254683621</v>
+        <v>0.9972797124207586</v>
       </c>
       <c r="H141" t="n">
-        <v>0.9792453388080554</v>
+        <v>0.9638705728733826</v>
       </c>
       <c r="I141" t="n">
-        <v>1.000068258098988</v>
+        <v>1.000200525613985</v>
       </c>
       <c r="J141" t="inlineStr">
         <is>
@@ -6106,13 +6106,13 @@
         <v>14889</v>
       </c>
       <c r="G142" t="n">
-        <v>0.9944415520156272</v>
+        <v>0.9942123609010742</v>
       </c>
       <c r="H142" t="n">
-        <v>0.8243560784246134</v>
+        <v>0.8224118261300054</v>
       </c>
       <c r="I142" t="n">
-        <v>1.038440410892263</v>
+        <v>1.0418537374248</v>
       </c>
       <c r="J142" t="inlineStr">
         <is>
@@ -6146,13 +6146,13 @@
         <v>15007</v>
       </c>
       <c r="G143" t="n">
-        <v>0.9940134680806701</v>
+        <v>0.9954611764608627</v>
       </c>
       <c r="H143" t="n">
-        <v>0.9457714538381964</v>
+        <v>0.9474916944613687</v>
       </c>
       <c r="I143" t="n">
-        <v>1.001315505897731</v>
+        <v>1.001122849358623</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
@@ -6186,13 +6186,13 @@
         <v>27060</v>
       </c>
       <c r="G144" t="n">
-        <v>0.9992831409813062</v>
+        <v>0.9988421717056313</v>
       </c>
       <c r="H144" t="n">
-        <v>0.9320076027052338</v>
+        <v>0.9285931413920101</v>
       </c>
       <c r="I144" t="n">
-        <v>1.003390278275356</v>
+        <v>1.003252330578494</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
@@ -6226,13 +6226,13 @@
         <v>3044</v>
       </c>
       <c r="G145" t="n">
-        <v>0.9992482708164966</v>
+        <v>0.9998091047740607</v>
       </c>
       <c r="H145" t="n">
-        <v>0.7937322327235248</v>
+        <v>0.7949065848924108</v>
       </c>
       <c r="I145" t="n">
-        <v>1.004699970752559</v>
+        <v>1.004352072643585</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -6266,13 +6266,13 @@
         <v>15146</v>
       </c>
       <c r="G146" t="n">
-        <v>0.8119884639830761</v>
+        <v>0.8216500955523126</v>
       </c>
       <c r="H146" t="n">
-        <v>0.916511042418836</v>
+        <v>0.9087653884968866</v>
       </c>
       <c r="I146" t="n">
-        <v>1.004808780304343</v>
+        <v>1.005243406106068</v>
       </c>
       <c r="J146" t="inlineStr">
         <is>
@@ -6306,13 +6306,13 @@
         <v>14955</v>
       </c>
       <c r="G147" t="n">
-        <v>0.9467451577761824</v>
+        <v>0.9502857938046688</v>
       </c>
       <c r="H147" t="n">
-        <v>0.9736856812017413</v>
+        <v>0.971127670917789</v>
       </c>
       <c r="I147" t="n">
-        <v>1.000825591916566</v>
+        <v>1.000870086642925</v>
       </c>
       <c r="J147" t="inlineStr">
         <is>
@@ -6346,13 +6346,13 @@
         <v>26950</v>
       </c>
       <c r="G148" t="n">
-        <v>0.9200386801046068</v>
+        <v>0.9233349128654328</v>
       </c>
       <c r="H148" t="n">
-        <v>0.9746280196214169</v>
+        <v>0.9729840219779432</v>
       </c>
       <c r="I148" t="n">
-        <v>1.001158315250087</v>
+        <v>1.001421363953763</v>
       </c>
       <c r="J148" t="inlineStr">
         <is>
@@ -6386,13 +6386,13 @@
         <v>2949</v>
       </c>
       <c r="G149" t="n">
-        <v>0.9127426511286715</v>
+        <v>0.9174882737485431</v>
       </c>
       <c r="H149" t="n">
-        <v>0.9054344951805421</v>
+        <v>0.9022164488157836</v>
       </c>
       <c r="I149" t="n">
-        <v>1.009342847787474</v>
+        <v>1.011777044901244</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
@@ -6426,13 +6426,13 @@
         <v>15025</v>
       </c>
       <c r="G150" t="n">
-        <v>0.8403815887253911</v>
+        <v>0.8485508924771544</v>
       </c>
       <c r="H150" t="n">
-        <v>0.814531546149683</v>
+        <v>0.818383675700735</v>
       </c>
       <c r="I150" t="n">
-        <v>1.01167377299329</v>
+        <v>1.009369992337251</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
@@ -6466,13 +6466,13 @@
         <v>14969</v>
       </c>
       <c r="G151" t="n">
-        <v>0.9625624323352961</v>
+        <v>0.9640316610702745</v>
       </c>
       <c r="H151" t="n">
-        <v>0.9454212011246045</v>
+        <v>0.9494421470244955</v>
       </c>
       <c r="I151" t="n">
-        <v>1.001206778248497</v>
+        <v>1.000768179188994</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
@@ -6506,13 +6506,13 @@
         <v>26930</v>
       </c>
       <c r="G152" t="n">
-        <v>0.9452132750521639</v>
+        <v>0.9482393818722621</v>
       </c>
       <c r="H152" t="n">
-        <v>0.9357159958944541</v>
+        <v>0.9410812913407181</v>
       </c>
       <c r="I152" t="n">
-        <v>1.000917284476358</v>
+        <v>1.000266479713529</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
@@ -6540,19 +6540,19 @@
         <v>1.2</v>
       </c>
       <c r="E153" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F153" t="n">
         <v>3076</v>
       </c>
       <c r="G153" t="n">
-        <v>0.8834419572908123</v>
+        <v>0.8897832202418889</v>
       </c>
       <c r="H153" t="n">
-        <v>0.8448363971593591</v>
+        <v>0.8234157061648495</v>
       </c>
       <c r="I153" t="n">
-        <v>1.006978703836246</v>
+        <v>1.011622237968025</v>
       </c>
       <c r="J153" t="inlineStr">
         <is>
@@ -6586,13 +6586,13 @@
         <v>15084</v>
       </c>
       <c r="G154" t="n">
-        <v>0.9983219173779738</v>
+        <v>0.9988229295421533</v>
       </c>
       <c r="H154" t="n">
-        <v>0.7561432629558517</v>
+        <v>0.7562440937019064</v>
       </c>
       <c r="I154" t="n">
-        <v>1.157630321903738</v>
+        <v>1.192884158529554</v>
       </c>
       <c r="J154" t="inlineStr">
         <is>
@@ -6626,13 +6626,13 @@
         <v>15155</v>
       </c>
       <c r="G155" t="n">
-        <v>0.9972656069741158</v>
+        <v>0.9972454445939483</v>
       </c>
       <c r="H155" t="n">
-        <v>0.9761399554364704</v>
+        <v>0.9758998656915895</v>
       </c>
       <c r="I155" t="n">
-        <v>1.000135964942849</v>
+        <v>1.000126656533413</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
@@ -6666,13 +6666,13 @@
         <v>26823</v>
       </c>
       <c r="G156" t="n">
-        <v>0.9986125119070717</v>
+        <v>0.9978923896628352</v>
       </c>
       <c r="H156" t="n">
-        <v>0.7814790635266511</v>
+        <v>0.7808514377414383</v>
       </c>
       <c r="I156" t="n">
-        <v>1.045586259206707</v>
+        <v>1.042414583916934</v>
       </c>
       <c r="J156" t="inlineStr">
         <is>
@@ -6706,13 +6706,13 @@
         <v>2938</v>
       </c>
       <c r="G157" t="n">
-        <v>0.9989353572478674</v>
+        <v>0.9983240092121749</v>
       </c>
       <c r="H157" t="n">
-        <v>0.9597160618076462</v>
+        <v>0.9679163359039963</v>
       </c>
       <c r="I157" t="n">
-        <v>1.000036680306975</v>
+        <v>1.00015531123622</v>
       </c>
       <c r="J157" t="inlineStr">
         <is>
@@ -6746,13 +6746,13 @@
         <v>14914</v>
       </c>
       <c r="G158" t="n">
-        <v>0.723773541968268</v>
+        <v>0.7362262141643963</v>
       </c>
       <c r="H158" t="n">
-        <v>0.8820706619531253</v>
+        <v>0.8724879331516023</v>
       </c>
       <c r="I158" t="n">
-        <v>1.010708955241519</v>
+        <v>1.01167373749089</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
@@ -6786,13 +6786,13 @@
         <v>15032</v>
       </c>
       <c r="G159" t="n">
-        <v>0.9751936517160587</v>
+        <v>0.9749395733645569</v>
       </c>
       <c r="H159" t="n">
-        <v>0.9692701093566823</v>
+        <v>0.970707861582817</v>
       </c>
       <c r="I159" t="n">
-        <v>1.000021346992408</v>
+        <v>0.999827143325507</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
@@ -6826,13 +6826,13 @@
         <v>27041</v>
       </c>
       <c r="G160" t="n">
-        <v>0.7358345194745709</v>
+        <v>0.7472829039602374</v>
       </c>
       <c r="H160" t="n">
-        <v>0.8950967402777507</v>
+        <v>0.8888407630695662</v>
       </c>
       <c r="I160" t="n">
-        <v>1.022033122504691</v>
+        <v>1.028254556447307</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
@@ -6866,13 +6866,13 @@
         <v>3013</v>
       </c>
       <c r="G161" t="n">
-        <v>0.9940039377726435</v>
+        <v>0.9959479523282617</v>
       </c>
       <c r="H161" t="n">
-        <v>0.952758651734402</v>
+        <v>0.9541401294637459</v>
       </c>
       <c r="I161" t="n">
-        <v>1.000302245459346</v>
+        <v>1.00034230860585</v>
       </c>
       <c r="J161" t="inlineStr">
         <is>
@@ -6906,13 +6906,13 @@
         <v>14885</v>
       </c>
       <c r="G162" t="n">
-        <v>0.7542278348848395</v>
+        <v>0.7671433346692916</v>
       </c>
       <c r="H162" t="n">
-        <v>0.7520153908245996</v>
+        <v>0.7450871943625037</v>
       </c>
       <c r="I162" t="n">
-        <v>1.027113481673406</v>
+        <v>1.02640555679147</v>
       </c>
       <c r="J162" t="inlineStr">
         <is>
@@ -6946,13 +6946,13 @@
         <v>15115</v>
       </c>
       <c r="G163" t="n">
-        <v>0.9368379985745487</v>
+        <v>0.9412034653801428</v>
       </c>
       <c r="H163" t="n">
-        <v>0.9545752057461642</v>
+        <v>0.9493946637492737</v>
       </c>
       <c r="I163" t="n">
-        <v>1.000458982423566</v>
+        <v>1.001417920733491</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
@@ -6980,23 +6980,23 @@
         <v>1.2</v>
       </c>
       <c r="E164" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F164" t="n">
         <v>27010</v>
       </c>
       <c r="G164" t="n">
-        <v>0.7191787828334686</v>
+        <v>0.7350016659038414</v>
       </c>
       <c r="H164" t="n">
-        <v>0.8144553827040351</v>
+        <v>0.7945345974783337</v>
       </c>
       <c r="I164" t="n">
-        <v>1.092430151973317</v>
+        <v>1.159966089517867</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>no bias</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -7026,13 +7026,13 @@
         <v>2990</v>
       </c>
       <c r="G165" t="n">
-        <v>0.9717698536595885</v>
+        <v>0.9736022517946273</v>
       </c>
       <c r="H165" t="n">
-        <v>0.9588501635412318</v>
+        <v>0.9550405541598449</v>
       </c>
       <c r="I165" t="n">
-        <v>1.000084463997353</v>
+        <v>1.000278808244053</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
@@ -7066,13 +7066,13 @@
         <v>15065</v>
       </c>
       <c r="G166" t="n">
-        <v>0.999616255837763</v>
+        <v>0.9995204485908085</v>
       </c>
       <c r="H166" t="n">
-        <v>0.83741443168173</v>
+        <v>0.8438674116969084</v>
       </c>
       <c r="I166" t="n">
-        <v>1.029272169329779</v>
+        <v>1.026809295556549</v>
       </c>
       <c r="J166" t="inlineStr">
         <is>
@@ -7106,13 +7106,13 @@
         <v>14975</v>
       </c>
       <c r="G167" t="n">
-        <v>0.9981698375812407</v>
+        <v>0.9991407811681392</v>
       </c>
       <c r="H167" t="n">
-        <v>0.9302663104644306</v>
+        <v>0.9232809985449357</v>
       </c>
       <c r="I167" t="n">
-        <v>1.002051017963185</v>
+        <v>1.002299040817617</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
@@ -7146,13 +7146,13 @@
         <v>27072</v>
       </c>
       <c r="G168" t="n">
-        <v>0.9998571547065909</v>
+        <v>0.9996212858482088</v>
       </c>
       <c r="H168" t="n">
-        <v>0.9105357366215264</v>
+        <v>0.9054730438304538</v>
       </c>
       <c r="I168" t="n">
-        <v>1.00639022785388</v>
+        <v>1.006793938479091</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -7180,19 +7180,19 @@
         <v>1</v>
       </c>
       <c r="E169" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F169" t="n">
         <v>2888</v>
       </c>
       <c r="G169" t="n">
-        <v>0.9951901898721001</v>
+        <v>0.9964108519562331</v>
       </c>
       <c r="H169" t="n">
-        <v>0.9453236005338665</v>
+        <v>0.8876928304178977</v>
       </c>
       <c r="I169" t="n">
-        <v>0.9999798914444323</v>
+        <v>1.004586990552708</v>
       </c>
       <c r="J169" t="inlineStr">
         <is>
@@ -7226,13 +7226,13 @@
         <v>15166</v>
       </c>
       <c r="G170" t="n">
-        <v>0.8192407184813217</v>
+        <v>0.8360402802892168</v>
       </c>
       <c r="H170" t="n">
-        <v>0.9330382127132942</v>
+        <v>0.9293521191519613</v>
       </c>
       <c r="I170" t="n">
-        <v>1.003836737757713</v>
+        <v>1.004007796130463</v>
       </c>
       <c r="J170" t="inlineStr">
         <is>
@@ -7266,13 +7266,13 @@
         <v>14922</v>
       </c>
       <c r="G171" t="n">
-        <v>0.9330204694448418</v>
+        <v>0.9317131092214592</v>
       </c>
       <c r="H171" t="n">
-        <v>0.9681173510518714</v>
+        <v>0.9671091793447185</v>
       </c>
       <c r="I171" t="n">
-        <v>1.001115137450362</v>
+        <v>1.001535872791875</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
@@ -7306,13 +7306,13 @@
         <v>26882</v>
       </c>
       <c r="G172" t="n">
-        <v>0.8901082205238824</v>
+        <v>0.8870362453328035</v>
       </c>
       <c r="H172" t="n">
-        <v>0.9634342843659774</v>
+        <v>0.9556026545336158</v>
       </c>
       <c r="I172" t="n">
-        <v>1.002848438585658</v>
+        <v>1.003894588941056</v>
       </c>
       <c r="J172" t="inlineStr">
         <is>
@@ -7337,22 +7337,22 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E173" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F173" t="n">
         <v>3030</v>
       </c>
       <c r="G173" t="n">
-        <v>0.9769690669529055</v>
+        <v>0.9340697478194249</v>
       </c>
       <c r="H173" t="n">
-        <v>0.9465091630127664</v>
+        <v>0.921507659456293</v>
       </c>
       <c r="I173" t="n">
-        <v>1.000003653955829</v>
+        <v>0.9998454825610791</v>
       </c>
       <c r="J173" t="inlineStr">
         <is>
@@ -7377,22 +7377,22 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E174" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F174" t="n">
         <v>14985</v>
       </c>
       <c r="G174" t="n">
-        <v>0.922732771418998</v>
+        <v>0.8409340786287354</v>
       </c>
       <c r="H174" t="n">
-        <v>0.8223167638409828</v>
+        <v>0.8746359632231343</v>
       </c>
       <c r="I174" t="n">
-        <v>1.041969298239209</v>
+        <v>1.01268603491926</v>
       </c>
       <c r="J174" t="inlineStr">
         <is>
@@ -7426,13 +7426,13 @@
         <v>15155</v>
       </c>
       <c r="G175" t="n">
-        <v>0.9577115549083061</v>
+        <v>0.9307793236566968</v>
       </c>
       <c r="H175" t="n">
-        <v>0.9192378856846969</v>
+        <v>0.9392183095494285</v>
       </c>
       <c r="I175" t="n">
-        <v>1.002612890667033</v>
+        <v>1.001677722413503</v>
       </c>
       <c r="J175" t="inlineStr">
         <is>
@@ -7466,13 +7466,13 @@
         <v>26883</v>
       </c>
       <c r="G176" t="n">
-        <v>0.9367195841045574</v>
+        <v>0.896296747007883</v>
       </c>
       <c r="H176" t="n">
-        <v>0.9025351740651818</v>
+        <v>0.9281988574311195</v>
       </c>
       <c r="I176" t="n">
-        <v>1.007712174840868</v>
+        <v>1.003690229179752</v>
       </c>
       <c r="J176" t="inlineStr">
         <is>
@@ -7500,19 +7500,19 @@
         <v>1.2</v>
       </c>
       <c r="E177" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F177" t="n">
         <v>2977</v>
       </c>
       <c r="G177" t="n">
-        <v>0.9244928467160334</v>
+        <v>0.9410901745196821</v>
       </c>
       <c r="H177" t="n">
-        <v>0.9444668271621072</v>
+        <v>0.9030722863900361</v>
       </c>
       <c r="I177" t="n">
-        <v>0.9998900891321751</v>
+        <v>1.001510792071854</v>
       </c>
       <c r="J177" t="inlineStr">
         <is>
@@ -7546,13 +7546,13 @@
         <v>14876</v>
       </c>
       <c r="G178" t="n">
-        <v>0.9974867253726223</v>
+        <v>0.9957795844999775</v>
       </c>
       <c r="H178" t="n">
-        <v>0.8824700462572509</v>
+        <v>0.9333001586030912</v>
       </c>
       <c r="I178" t="n">
-        <v>1.010922065180296</v>
+        <v>1.002493031512576</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
@@ -7586,13 +7586,13 @@
         <v>15052</v>
       </c>
       <c r="G179" t="n">
-        <v>0.998610590376364</v>
+        <v>0.9992745133170408</v>
       </c>
       <c r="H179" t="n">
-        <v>0.8851232924486806</v>
+        <v>0.8415217430044452</v>
       </c>
       <c r="I179" t="n">
-        <v>1.005691937818565</v>
+        <v>1.010868856042908</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
@@ -7620,19 +7620,19 @@
         <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F180" t="n">
         <v>27062</v>
       </c>
       <c r="G180" t="n">
-        <v>0.9965279646459908</v>
+        <v>0.9944069845581788</v>
       </c>
       <c r="H180" t="n">
-        <v>0.9853592461935188</v>
+        <v>0.911378938333364</v>
       </c>
       <c r="I180" t="n">
-        <v>1.000016752467256</v>
+        <v>1.008117790786405</v>
       </c>
       <c r="J180" t="inlineStr">
         <is>
@@ -7666,13 +7666,13 @@
         <v>3010</v>
       </c>
       <c r="G181" t="n">
-        <v>0.9942977644894654</v>
+        <v>0.9941584615754212</v>
       </c>
       <c r="H181" t="n">
-        <v>0.9257832819334618</v>
+        <v>0.8919028472841306</v>
       </c>
       <c r="I181" t="n">
-        <v>1.000178414345053</v>
+        <v>1.000163046115539</v>
       </c>
       <c r="J181" t="inlineStr">
         <is>
@@ -7706,13 +7706,13 @@
         <v>15113</v>
       </c>
       <c r="G182" t="n">
-        <v>0.8759234808630245</v>
+        <v>0.9350645416864305</v>
       </c>
       <c r="H182" t="n">
-        <v>0.9504058174156438</v>
+        <v>0.9710303972810891</v>
       </c>
       <c r="I182" t="n">
-        <v>1.001804117758618</v>
+        <v>1.000503903404266</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
@@ -7746,13 +7746,13 @@
         <v>14969</v>
       </c>
       <c r="G183" t="n">
-        <v>0.8901764105805288</v>
+        <v>0.8534418988114959</v>
       </c>
       <c r="H183" t="n">
-        <v>0.9466644120432551</v>
+        <v>0.9229862062709724</v>
       </c>
       <c r="I183" t="n">
-        <v>1.003248148637948</v>
+        <v>1.009136075942807</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
@@ -7777,22 +7777,22 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E184" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F184" t="n">
         <v>27036</v>
       </c>
       <c r="G184" t="n">
-        <v>0.9949572888065091</v>
+        <v>0.904683874333883</v>
       </c>
       <c r="H184" t="n">
-        <v>0.9786185911676214</v>
+        <v>0.9460750748923167</v>
       </c>
       <c r="I184" t="n">
-        <v>1.000102128565427</v>
+        <v>1.003412301198009</v>
       </c>
       <c r="J184" t="inlineStr">
         <is>
@@ -7826,13 +7826,13 @@
         <v>2882</v>
       </c>
       <c r="G185" t="n">
-        <v>0.9586237426108575</v>
+        <v>0.9429692026768146</v>
       </c>
       <c r="H185" t="n">
-        <v>0.9488640567908604</v>
+        <v>0.934272317831454</v>
       </c>
       <c r="I185" t="n">
-        <v>1.000722246062257</v>
+        <v>1.002928852609763</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
@@ -7857,22 +7857,22 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E186" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F186" t="n">
         <v>15002</v>
       </c>
       <c r="G186" t="n">
-        <v>0.9858539667624947</v>
+        <v>0.9339770268267673</v>
       </c>
       <c r="H186" t="n">
-        <v>0.8667992998932054</v>
+        <v>0.9402121214477099</v>
       </c>
       <c r="I186" t="n">
-        <v>1.012959399995884</v>
+        <v>1.000851871455792</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
@@ -7906,13 +7906,13 @@
         <v>14883</v>
       </c>
       <c r="G187" t="n">
-        <v>0.8687699099202048</v>
+        <v>0.8520574280598137</v>
       </c>
       <c r="H187" t="n">
-        <v>0.863706448410171</v>
+        <v>0.8673371109831508</v>
       </c>
       <c r="I187" t="n">
-        <v>1.005084219868593</v>
+        <v>1.003343697588087</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
@@ -7940,19 +7940,19 @@
         <v>1.2</v>
       </c>
       <c r="E188" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F188" t="n">
         <v>27086</v>
       </c>
       <c r="G188" t="n">
-        <v>0.8495498160496485</v>
+        <v>0.9015001180064557</v>
       </c>
       <c r="H188" t="n">
-        <v>0.9794497124669742</v>
+        <v>0.9311054518232048</v>
       </c>
       <c r="I188" t="n">
-        <v>1.000151347651749</v>
+        <v>1.002542303133815</v>
       </c>
       <c r="J188" t="inlineStr">
         <is>
@@ -7986,13 +7986,13 @@
         <v>3029</v>
       </c>
       <c r="G189" t="n">
-        <v>0.9448802921828854</v>
+        <v>0.9373640211222204</v>
       </c>
       <c r="H189" t="n">
-        <v>0.887143575685196</v>
+        <v>0.8958908377136039</v>
       </c>
       <c r="I189" t="n">
-        <v>1.000429096147979</v>
+        <v>0.9997216697373205</v>
       </c>
       <c r="J189" t="inlineStr">
         <is>
@@ -8026,13 +8026,13 @@
         <v>14980</v>
       </c>
       <c r="G190" t="n">
-        <v>0.9967234799732608</v>
+        <v>0.9968968413343047</v>
       </c>
       <c r="H190" t="n">
-        <v>0.8965899060293736</v>
+        <v>0.8965974878518146</v>
       </c>
       <c r="I190" t="n">
-        <v>1.00423376775405</v>
+        <v>1.003910334603911</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
@@ -8066,13 +8066,13 @@
         <v>14837</v>
       </c>
       <c r="G191" t="n">
-        <v>0.9966657550960653</v>
+        <v>0.9961293820617673</v>
       </c>
       <c r="H191" t="n">
-        <v>0.8970991223302343</v>
+        <v>0.8967957882848209</v>
       </c>
       <c r="I191" t="n">
-        <v>1.004931034169262</v>
+        <v>1.004292366853038</v>
       </c>
       <c r="J191" t="inlineStr">
         <is>
@@ -8106,13 +8106,13 @@
         <v>27016</v>
       </c>
       <c r="G192" t="n">
-        <v>0.9983962629125909</v>
+        <v>0.9988647755675754</v>
       </c>
       <c r="H192" t="n">
-        <v>0.8141571543074487</v>
+        <v>0.8137516940784132</v>
       </c>
       <c r="I192" t="n">
-        <v>1.074809184539467</v>
+        <v>1.075148655700372</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
@@ -8146,13 +8146,13 @@
         <v>3167</v>
       </c>
       <c r="G193" t="n">
-        <v>0.9963405695612738</v>
+        <v>0.9960125356906853</v>
       </c>
       <c r="H193" t="n">
-        <v>0.7682951949660248</v>
+        <v>0.7675460493308965</v>
       </c>
       <c r="I193" t="n">
-        <v>1.005955728552087</v>
+        <v>1.004756013516653</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
@@ -8186,13 +8186,13 @@
         <v>14889</v>
       </c>
       <c r="G194" t="n">
-        <v>0.9007805089256351</v>
+        <v>0.9048046270350346</v>
       </c>
       <c r="H194" t="n">
-        <v>0.9565844543704868</v>
+        <v>0.9500601800448771</v>
       </c>
       <c r="I194" t="n">
-        <v>1.001635570862275</v>
+        <v>1.00206400879622</v>
       </c>
       <c r="J194" t="inlineStr">
         <is>
@@ -8226,13 +8226,13 @@
         <v>15216</v>
       </c>
       <c r="G195" t="n">
-        <v>0.904980584730079</v>
+        <v>0.9080292043798411</v>
       </c>
       <c r="H195" t="n">
-        <v>0.9620473797814559</v>
+        <v>0.9557328817322808</v>
       </c>
       <c r="I195" t="n">
-        <v>1.001423010483723</v>
+        <v>1.001959133928839</v>
       </c>
       <c r="J195" t="inlineStr">
         <is>
@@ -8266,13 +8266,13 @@
         <v>26926</v>
       </c>
       <c r="G196" t="n">
-        <v>0.7851763538256336</v>
+        <v>0.7935338230313058</v>
       </c>
       <c r="H196" t="n">
-        <v>0.9231816498968289</v>
+        <v>0.9126604002270526</v>
       </c>
       <c r="I196" t="n">
-        <v>1.008584518374175</v>
+        <v>1.010313312218591</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
@@ -8306,13 +8306,13 @@
         <v>2969</v>
       </c>
       <c r="G197" t="n">
-        <v>0.8955645344708607</v>
+        <v>0.9006006067740565</v>
       </c>
       <c r="H197" t="n">
-        <v>0.9062629202259835</v>
+        <v>0.8916439788459627</v>
       </c>
       <c r="I197" t="n">
-        <v>1.012973861321344</v>
+        <v>1.019731982580142</v>
       </c>
       <c r="J197" t="inlineStr">
         <is>
@@ -8346,13 +8346,13 @@
         <v>14972</v>
       </c>
       <c r="G198" t="n">
-        <v>0.9209935397221699</v>
+        <v>0.9239573331560521</v>
       </c>
       <c r="H198" t="n">
-        <v>0.8921209311008816</v>
+        <v>0.8977006577227916</v>
       </c>
       <c r="I198" t="n">
-        <v>1.005869367595535</v>
+        <v>1.004409162944197</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
@@ -8386,13 +8386,13 @@
         <v>15087</v>
       </c>
       <c r="G199" t="n">
-        <v>0.9263509953679503</v>
+        <v>0.9305530716123638</v>
       </c>
       <c r="H199" t="n">
-        <v>0.8964514329041613</v>
+        <v>0.9013755406336467</v>
       </c>
       <c r="I199" t="n">
-        <v>1.005249629337099</v>
+        <v>1.003792979788682</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
@@ -8426,13 +8426,13 @@
         <v>26955</v>
       </c>
       <c r="G200" t="n">
-        <v>0.8040311745506569</v>
+        <v>0.8135791399852927</v>
       </c>
       <c r="H200" t="n">
-        <v>0.7898110578905502</v>
+        <v>0.7946435325063507</v>
       </c>
       <c r="I200" t="n">
-        <v>1.034518750682674</v>
+        <v>1.029417939199745</v>
       </c>
       <c r="J200" t="inlineStr">
         <is>
@@ -8460,23 +8460,23 @@
         <v>1.2</v>
       </c>
       <c r="E201" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F201" t="n">
         <v>2986</v>
       </c>
       <c r="G201" t="n">
-        <v>0.8558992292170211</v>
+        <v>0.8634578210132631</v>
       </c>
       <c r="H201" t="n">
-        <v>0.801086847557116</v>
+        <v>0.7834432162333197</v>
       </c>
       <c r="I201" t="n">
-        <v>1.018968942719658</v>
+        <v>1.030389118291737</v>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>no bias</t>
+          <t>positive</t>
         </is>
       </c>
     </row>
@@ -8506,13 +8506,13 @@
         <v>14987</v>
       </c>
       <c r="G202" t="n">
-        <v>0.9991196487060813</v>
+        <v>0.9988479379570274</v>
       </c>
       <c r="H202" t="n">
-        <v>0.8950441266067569</v>
+        <v>0.8874892016075059</v>
       </c>
       <c r="I202" t="n">
-        <v>1.004645176045163</v>
+        <v>1.004595210654458</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
@@ -8546,13 +8546,13 @@
         <v>15093</v>
       </c>
       <c r="G203" t="n">
-        <v>0.9970763419880185</v>
+        <v>0.9969379240651367</v>
       </c>
       <c r="H203" t="n">
-        <v>0.8797279122311414</v>
+        <v>0.8749992752408876</v>
       </c>
       <c r="I203" t="n">
-        <v>1.006854166993257</v>
+        <v>1.006986890238666</v>
       </c>
       <c r="J203" t="inlineStr">
         <is>
@@ -8586,13 +8586,13 @@
         <v>26912</v>
       </c>
       <c r="G204" t="n">
-        <v>0.9994371249823941</v>
+        <v>0.9993865934964485</v>
       </c>
       <c r="H204" t="n">
-        <v>0.838705319104585</v>
+        <v>0.8451940496118936</v>
       </c>
       <c r="I204" t="n">
-        <v>1.044020708486789</v>
+        <v>1.036807200406401</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
@@ -8620,19 +8620,19 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F205" t="n">
         <v>3008</v>
       </c>
       <c r="G205" t="n">
-        <v>0.9972158791708399</v>
+        <v>0.9975948162331117</v>
       </c>
       <c r="H205" t="n">
-        <v>0.9642779924153831</v>
+        <v>0.9218558740020066</v>
       </c>
       <c r="I205" t="n">
-        <v>1.000432223197954</v>
+        <v>1.003097323828962</v>
       </c>
       <c r="J205" t="inlineStr">
         <is>
@@ -8666,13 +8666,13 @@
         <v>15027</v>
       </c>
       <c r="G206" t="n">
-        <v>0.8839717193954029</v>
+        <v>0.8837868867072191</v>
       </c>
       <c r="H206" t="n">
-        <v>0.9578457155157054</v>
+        <v>0.9497091900449486</v>
       </c>
       <c r="I206" t="n">
-        <v>1.002727966271641</v>
+        <v>1.003868070869232</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
@@ -8706,13 +8706,13 @@
         <v>15063</v>
       </c>
       <c r="G207" t="n">
-        <v>0.8868434002397531</v>
+        <v>0.8873336020976413</v>
       </c>
       <c r="H207" t="n">
-        <v>0.957730873003604</v>
+        <v>0.9507529999631629</v>
       </c>
       <c r="I207" t="n">
-        <v>1.001869320340596</v>
+        <v>1.002656149641286</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
@@ -8746,13 +8746,13 @@
         <v>26915</v>
       </c>
       <c r="G208" t="n">
-        <v>0.8038340404993489</v>
+        <v>0.8226781226053784</v>
       </c>
       <c r="H208" t="n">
-        <v>0.9359062105751389</v>
+        <v>0.9312278566990512</v>
       </c>
       <c r="I208" t="n">
-        <v>1.006537493522951</v>
+        <v>1.006709337155234</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
@@ -8777,22 +8777,22 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E209" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F209" t="n">
         <v>2995</v>
       </c>
       <c r="G209" t="n">
-        <v>0.9918471167735109</v>
+        <v>0.9494193485583814</v>
       </c>
       <c r="H209" t="n">
-        <v>0.9706110399043563</v>
+        <v>0.9539659205167951</v>
       </c>
       <c r="I209" t="n">
-        <v>1.000014830668141</v>
+        <v>0.9999464414861324</v>
       </c>
       <c r="J209" t="inlineStr">
         <is>
@@ -8826,13 +8826,13 @@
         <v>14910</v>
       </c>
       <c r="G210" t="n">
-        <v>0.932666062055225</v>
+        <v>0.8887822791861125</v>
       </c>
       <c r="H210" t="n">
-        <v>0.8731008768548035</v>
+        <v>0.9075501626061833</v>
       </c>
       <c r="I210" t="n">
-        <v>1.006719537699035</v>
+        <v>1.001747393445785</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
@@ -8866,13 +8866,13 @@
         <v>15009</v>
       </c>
       <c r="G211" t="n">
-        <v>0.9322007804784617</v>
+        <v>0.8894323334432166</v>
       </c>
       <c r="H211" t="n">
-        <v>0.870254737017264</v>
+        <v>0.9051945305923422</v>
       </c>
       <c r="I211" t="n">
-        <v>1.007203688922701</v>
+        <v>1.002424494103296</v>
       </c>
       <c r="J211" t="inlineStr">
         <is>
@@ -8897,22 +8897,22 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E212" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F212" t="n">
         <v>27116</v>
       </c>
       <c r="G212" t="n">
-        <v>0.9125141828640116</v>
+        <v>0.8258020424055192</v>
       </c>
       <c r="H212" t="n">
-        <v>0.8247752067845968</v>
+        <v>0.880086984710401</v>
       </c>
       <c r="I212" t="n">
-        <v>1.061362090623906</v>
+        <v>1.017910531287821</v>
       </c>
       <c r="J212" t="inlineStr">
         <is>
@@ -8940,19 +8940,19 @@
         <v>1.2</v>
       </c>
       <c r="E213" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F213" t="n">
         <v>2965</v>
       </c>
       <c r="G213" t="n">
-        <v>0.931154224050317</v>
+        <v>0.9573067474102338</v>
       </c>
       <c r="H213" t="n">
-        <v>0.9666490543006897</v>
+        <v>0.9123885838766307</v>
       </c>
       <c r="I213" t="n">
-        <v>1.000006183946778</v>
+        <v>1.00089666784779</v>
       </c>
       <c r="J213" t="inlineStr">
         <is>
@@ -8986,13 +8986,13 @@
         <v>14938</v>
       </c>
       <c r="G214" t="n">
-        <v>0.9990330313771916</v>
+        <v>0.9985658139715855</v>
       </c>
       <c r="H214" t="n">
-        <v>0.7966906113281328</v>
+        <v>0.7971106277276441</v>
       </c>
       <c r="I214" t="n">
-        <v>1.069275836801562</v>
+        <v>1.075288570530475</v>
       </c>
       <c r="J214" t="inlineStr">
         <is>
@@ -9026,13 +9026,13 @@
         <v>15174</v>
       </c>
       <c r="G215" t="n">
-        <v>0.9988535440336811</v>
+        <v>0.9983569147381116</v>
       </c>
       <c r="H215" t="n">
-        <v>0.7971308808128006</v>
+        <v>0.7982126105568572</v>
       </c>
       <c r="I215" t="n">
-        <v>1.021898741004967</v>
+        <v>1.019701328916434</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>
@@ -9066,13 +9066,13 @@
         <v>26903</v>
       </c>
       <c r="G216" t="n">
-        <v>0.999196032141431</v>
+        <v>0.9985853365486308</v>
       </c>
       <c r="H216" t="n">
-        <v>0.9850580111045883</v>
+        <v>0.9813047638372507</v>
       </c>
       <c r="I216" t="n">
-        <v>1.00014275147099</v>
+        <v>1.000139625169534</v>
       </c>
       <c r="J216" t="inlineStr">
         <is>
@@ -9106,13 +9106,13 @@
         <v>2985</v>
       </c>
       <c r="G217" t="n">
-        <v>0.9976239042625706</v>
+        <v>0.9970987323102786</v>
       </c>
       <c r="H217" t="n">
-        <v>0.9755357642865649</v>
+        <v>0.9679575928003721</v>
       </c>
       <c r="I217" t="n">
-        <v>1.000016829903805</v>
+        <v>1.000002255299426</v>
       </c>
       <c r="J217" t="inlineStr">
         <is>
@@ -9146,13 +9146,13 @@
         <v>14748</v>
       </c>
       <c r="G218" t="n">
-        <v>0.7725542214056909</v>
+        <v>0.7849325604105214</v>
       </c>
       <c r="H218" t="n">
-        <v>0.8970921492218493</v>
+        <v>0.8902976235267058</v>
       </c>
       <c r="I218" t="n">
-        <v>1.007235973894132</v>
+        <v>1.007562847646483</v>
       </c>
       <c r="J218" t="inlineStr">
         <is>
@@ -9186,13 +9186,13 @@
         <v>15248</v>
       </c>
       <c r="G219" t="n">
-        <v>0.792582641662599</v>
+        <v>0.8036235227803915</v>
       </c>
       <c r="H219" t="n">
-        <v>0.9114897458711392</v>
+        <v>0.9012865409038496</v>
       </c>
       <c r="I219" t="n">
-        <v>1.014482607865242</v>
+        <v>1.018418538815344</v>
       </c>
       <c r="J219" t="inlineStr">
         <is>
@@ -9226,13 +9226,13 @@
         <v>27022</v>
       </c>
       <c r="G220" t="n">
-        <v>0.9872169201442187</v>
+        <v>0.9881838070342348</v>
       </c>
       <c r="H220" t="n">
-        <v>0.9796525353471708</v>
+        <v>0.9796904665100582</v>
       </c>
       <c r="I220" t="n">
-        <v>1.00023850151491</v>
+        <v>1.000245885449039</v>
       </c>
       <c r="J220" t="inlineStr">
         <is>
@@ -9266,13 +9266,13 @@
         <v>2982</v>
       </c>
       <c r="G221" t="n">
-        <v>0.9941778315753069</v>
+        <v>0.9943695620577533</v>
       </c>
       <c r="H221" t="n">
-        <v>0.9517219166818652</v>
+        <v>0.9701810507551755</v>
       </c>
       <c r="I221" t="n">
-        <v>1.000104921654311</v>
+        <v>1.00010595146537</v>
       </c>
       <c r="J221" t="inlineStr">
         <is>
@@ -9306,13 +9306,13 @@
         <v>15212</v>
       </c>
       <c r="G222" t="n">
-        <v>0.7952381364144019</v>
+        <v>0.8057458157404972</v>
       </c>
       <c r="H222" t="n">
-        <v>0.7751333001823371</v>
+        <v>0.7750554189293265</v>
       </c>
       <c r="I222" t="n">
-        <v>1.021264524559939</v>
+        <v>1.019253653607562</v>
       </c>
       <c r="J222" t="inlineStr">
         <is>
@@ -9340,19 +9340,19 @@
         <v>1.2</v>
       </c>
       <c r="E223" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F223" t="n">
         <v>14845</v>
       </c>
       <c r="G223" t="n">
-        <v>0.7643305897555595</v>
+        <v>0.774719668075129</v>
       </c>
       <c r="H223" t="n">
-        <v>0.8311709175410437</v>
+        <v>0.8107310801199655</v>
       </c>
       <c r="I223" t="n">
-        <v>1.034189279052847</v>
+        <v>1.05271040037143</v>
       </c>
       <c r="J223" t="inlineStr">
         <is>
@@ -9386,13 +9386,13 @@
         <v>26962</v>
       </c>
       <c r="G224" t="n">
-        <v>0.9797351436381923</v>
+        <v>0.9800046763241766</v>
       </c>
       <c r="H224" t="n">
-        <v>0.9387397727107167</v>
+        <v>0.9478969221312822</v>
       </c>
       <c r="I224" t="n">
-        <v>1.000130777312709</v>
+        <v>1.00054968022705</v>
       </c>
       <c r="J224" t="inlineStr">
         <is>
@@ -9426,13 +9426,13 @@
         <v>2981</v>
       </c>
       <c r="G225" t="n">
-        <v>0.9883321734287214</v>
+        <v>0.9873092729924787</v>
       </c>
       <c r="H225" t="n">
-        <v>0.9610894453785878</v>
+        <v>0.9533077708902121</v>
       </c>
       <c r="I225" t="n">
-        <v>1.000081051106933</v>
+        <v>0.9999574041638839</v>
       </c>
       <c r="J225" t="inlineStr">
         <is>
@@ -9466,13 +9466,13 @@
         <v>14920</v>
       </c>
       <c r="G226" t="n">
-        <v>0.9973549820108287</v>
+        <v>0.9964490633086359</v>
       </c>
       <c r="H226" t="n">
-        <v>0.8596037419618464</v>
+        <v>0.8866025659783782</v>
       </c>
       <c r="I226" t="n">
-        <v>1.02049511969086</v>
+        <v>1.011046374462978</v>
       </c>
       <c r="J226" t="inlineStr">
         <is>
@@ -9500,19 +9500,19 @@
         <v>1</v>
       </c>
       <c r="E227" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F227" t="n">
         <v>15154</v>
       </c>
       <c r="G227" t="n">
-        <v>0.9919709929768724</v>
+        <v>0.9934637496048949</v>
       </c>
       <c r="H227" t="n">
-        <v>0.9657964382991535</v>
+        <v>0.8897419868441744</v>
       </c>
       <c r="I227" t="n">
-        <v>1.000734199141683</v>
+        <v>1.009933746419761</v>
       </c>
       <c r="J227" t="inlineStr">
         <is>
@@ -9546,13 +9546,13 @@
         <v>26929</v>
       </c>
       <c r="G228" t="n">
-        <v>0.9948492935577481</v>
+        <v>0.9965737978117111</v>
       </c>
       <c r="H228" t="n">
-        <v>0.8823441599956531</v>
+        <v>0.8475660686059964</v>
       </c>
       <c r="I228" t="n">
-        <v>1.012240218283722</v>
+        <v>1.019733630904754</v>
       </c>
       <c r="J228" t="inlineStr">
         <is>
@@ -9586,13 +9586,13 @@
         <v>2997</v>
       </c>
       <c r="G229" t="n">
-        <v>0.9990055694228004</v>
+        <v>0.9981681194285106</v>
       </c>
       <c r="H229" t="n">
-        <v>0.9057861511922253</v>
+        <v>0.8839036107901934</v>
       </c>
       <c r="I229" t="n">
-        <v>1.000668253361305</v>
+        <v>1.000773064022066</v>
       </c>
       <c r="J229" t="inlineStr">
         <is>
@@ -9626,13 +9626,13 @@
         <v>14941</v>
       </c>
       <c r="G230" t="n">
-        <v>0.8586720946480003</v>
+        <v>0.8968244925500838</v>
       </c>
       <c r="H230" t="n">
-        <v>0.941720440484106</v>
+        <v>0.9478892294581136</v>
       </c>
       <c r="I230" t="n">
-        <v>1.002552014778549</v>
+        <v>1.001806081172493</v>
       </c>
       <c r="J230" t="inlineStr">
         <is>
@@ -9657,22 +9657,22 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E231" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="F231" t="n">
         <v>14774</v>
       </c>
       <c r="G231" t="n">
-        <v>0.9649208123637663</v>
+        <v>0.8847639310150071</v>
       </c>
       <c r="H231" t="n">
-        <v>0.9719659439552139</v>
+        <v>0.933326337175597</v>
       </c>
       <c r="I231" t="n">
-        <v>1.000258393887781</v>
+        <v>1.002337393443306</v>
       </c>
       <c r="J231" t="inlineStr">
         <is>
@@ -9706,13 +9706,13 @@
         <v>27232</v>
       </c>
       <c r="G232" t="n">
-        <v>0.8639987412867687</v>
+        <v>0.8315046805781925</v>
       </c>
       <c r="H232" t="n">
-        <v>0.9434856784024938</v>
+        <v>0.9204090470873331</v>
       </c>
       <c r="I232" t="n">
-        <v>1.005639973209047</v>
+        <v>1.011760622674417</v>
       </c>
       <c r="J232" t="inlineStr">
         <is>
@@ -9746,13 +9746,13 @@
         <v>3053</v>
       </c>
       <c r="G233" t="n">
-        <v>0.9612374007402272</v>
+        <v>0.9527900276337391</v>
       </c>
       <c r="H233" t="n">
-        <v>0.9601450395343203</v>
+        <v>0.9479741568388012</v>
       </c>
       <c r="I233" t="n">
-        <v>1.00018603737664</v>
+        <v>1.000610581806407</v>
       </c>
       <c r="J233" t="inlineStr">
         <is>
@@ -9777,22 +9777,22 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="E234" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="F234" t="n">
         <v>15178</v>
       </c>
       <c r="G234" t="n">
-        <v>0.9697464765045914</v>
+        <v>0.890848996969953</v>
       </c>
       <c r="H234" t="n">
-        <v>0.84962198432209</v>
+        <v>0.9095681123607084</v>
       </c>
       <c r="I234" t="n">
-        <v>1.022386568680485</v>
+        <v>1.004348865007659</v>
       </c>
       <c r="J234" t="inlineStr">
         <is>
@@ -9820,19 +9820,19 @@
         <v>1.2</v>
       </c>
       <c r="E235" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="F235" t="n">
         <v>14871</v>
       </c>
       <c r="G235" t="n">
-        <v>0.8569900774467178</v>
+        <v>0.8938642023164798</v>
       </c>
       <c r="H235" t="n">
-        <v>0.9565098264361963</v>
+        <v>0.9132772502876682</v>
       </c>
       <c r="I235" t="n">
-        <v>1.000061125896042</v>
+        <v>1.003115510818098</v>
       </c>
       <c r="J235" t="inlineStr">
         <is>
@@ -9866,13 +9866,13 @@
         <v>26905</v>
       </c>
       <c r="G236" t="n">
-        <v>0.8654605323771617</v>
+        <v>0.8323578257518154</v>
       </c>
       <c r="H236" t="n">
-        <v>0.8623814050641092</v>
+        <v>0.876857761322303</v>
       </c>
       <c r="I236" t="n">
-        <v>1.01372961261674</v>
+        <v>1.008388215129216</v>
       </c>
       <c r="J236" t="inlineStr">
         <is>
@@ -9906,13 +9906,13 @@
         <v>3046</v>
       </c>
       <c r="G237" t="n">
-        <v>0.9636145961314352</v>
+        <v>0.9548969010743543</v>
       </c>
       <c r="H237" t="n">
-        <v>0.9082490629080842</v>
+        <v>0.9250101511422717</v>
       </c>
       <c r="I237" t="n">
-        <v>1.000019169507652</v>
+        <v>0.999448460686897</v>
       </c>
       <c r="J237" t="inlineStr">
         <is>
